--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-29).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-29).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 9.145,61</t>
+    <t>R$ 9.106,92</t>
   </si>
   <si>
-    <t>96.2</t>
+    <t>95.8</t>
   </si>
   <si>
     <t>61.0</t>
   </si>
   <si>
-    <t>6.17</t>
+    <t>6.18</t>
   </si>
   <si>
-    <t>20.0</t>
+    <t>20.1</t>
   </si>
   <si>
-    <t>7.1</t>
+    <t>7.2</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>34.1%</t>
+    <t>34.3%</t>
   </si>
   <si>
     <t>15.8%</t>
@@ -6852,7 +6852,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6882,14 +6882,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>7174.5299999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>81</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.8942382716049382</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>20.78358208955224</v>
+      </c>
+      <c r="R36" s="8">
+        <v>7.5156716417910445</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.26865671641791045</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9141,7 +9153,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9171,14 +9183,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1239.5</v>
+      </c>
+      <c r="N51" s="6">
+        <v>12</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>6.0430583333333336</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>21.308333333333334</v>
+      </c>
+      <c r="R51" s="8">
+        <v>8.0416666666666661</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14831,7 +14855,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14859,14 +14883,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>11478.18</v>
+      </c>
+      <c r="N89" s="6">
+        <v>109</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>8.3888891891891895</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>26.196665714285714</v>
+      </c>
+      <c r="R89" s="8">
+        <v>9.1382352941176475</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.057142857142857141</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
